--- a/backend/Sonidos de mi tierra.xlsx
+++ b/backend/Sonidos de mi tierra.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="338">
   <si>
     <t>id</t>
   </si>
@@ -532,6 +532,30 @@
   </si>
   <si>
     <t>Una pieza épica y solemne que musicaliza la figura histórica de Sandino, convirtiéndose en un referente de la canción testimonial.</t>
+  </si>
+  <si>
+    <t>El Gueguense</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RZwW42sv0to?si=FZtcUnqaMO2HXiif</t>
+  </si>
+  <si>
+    <t>Obra Maestra del Patrimonio Oral e Inmaterial de la Humanidad. Es una comedia bailete de la época colonial.</t>
+  </si>
+  <si>
+    <t>El viejo y la vieja</t>
+  </si>
+  <si>
+    <t>1900</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MnrBNa1m1Ao?si=ztOkR8Tm4yq3FZc_</t>
+  </si>
+  <si>
+    <t>Son alegre del folklore nicaragüense que retrata, con picardía y humor campesino, la eterna discusión entre un matrimonio de viejitos. Entre bromas, baile y ritmo festivo, la canción refleja la tradición popular que anima fiestas patronales y celebraciones culturales en Nicaragua.</t>
   </si>
   <si>
     <t>photo_url</t>
@@ -1597,7 +1621,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B17" displayName="Table8" name="Table8" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B19" displayName="Table8" name="Table8" id="6">
   <tableColumns count="2">
     <tableColumn name="song_id" id="1"/>
     <tableColumn name="genre_id" id="2"/>
@@ -1607,7 +1631,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B48" displayName="Table3" name="Table3" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B56" displayName="Table3" name="Table3" id="7">
   <tableColumns count="2">
     <tableColumn name="song_id" id="1"/>
     <tableColumn name="tag_id" id="2"/>
@@ -1617,7 +1641,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B28" displayName="Table4" name="Table4" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B32" displayName="Table4" name="Table4" id="8">
   <tableColumns count="2">
     <tableColumn name="song_id" id="1"/>
     <tableColumn name="region_id" id="2"/>
@@ -2657,25 +2681,57 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="28"/>
+      <c r="A18" s="25">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="27">
+        <v>1500.0</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>174</v>
+      </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="28"/>
+      <c r="A19" s="25">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="27">
+        <v>1900.0</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>178</v>
+      </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
@@ -2736,13 +2792,15 @@
     <hyperlink r:id="rId14" ref="G15"/>
     <hyperlink r:id="rId15" ref="G16"/>
     <hyperlink r:id="rId16" ref="G17"/>
+    <hyperlink r:id="rId17" ref="G18"/>
+    <hyperlink r:id="rId18" ref="G19"/>
   </hyperlinks>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId19"/>
   <tableParts count="1">
-    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2775,25 +2833,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="J1" s="7"/>
     </row>
@@ -2802,26 +2860,26 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F2" s="33"/>
       <c r="G2" s="10" t="s">
         <v>64</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -2830,28 +2888,28 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="J3" s="7"/>
     </row>
@@ -2860,26 +2918,26 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F4" s="33"/>
       <c r="G4" s="10" t="s">
         <v>64</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J4" s="7"/>
     </row>
@@ -2888,16 +2946,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>164</v>
@@ -2906,10 +2964,10 @@
         <v>20</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="J5" s="7"/>
     </row>
@@ -2918,28 +2976,28 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="J6" s="7"/>
     </row>
@@ -2948,28 +3006,28 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>4</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J7" s="7"/>
     </row>
@@ -2978,13 +3036,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E8" s="33"/>
       <c r="F8" s="33"/>
@@ -2992,10 +3050,10 @@
         <v>68</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="J8" s="7"/>
     </row>
@@ -3004,13 +3062,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>106</v>
@@ -3020,10 +3078,10 @@
         <v>60</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J9" s="7"/>
     </row>
@@ -3032,26 +3090,26 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F10" s="33"/>
       <c r="G10" s="10" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="J10" s="7"/>
     </row>
@@ -3060,26 +3118,26 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="28" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J11" s="7"/>
     </row>
@@ -3088,26 +3146,26 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F12" s="38"/>
       <c r="G12" s="28" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -3115,26 +3173,26 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F13" s="41"/>
       <c r="G13" s="22" t="s">
         <v>64</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -3142,28 +3200,28 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
@@ -3227,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D1" s="44" t="s">
         <v>3</v>
@@ -3238,13 +3296,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -3252,13 +3310,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -3266,13 +3324,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -3280,13 +3338,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -3294,13 +3352,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="D6" s="46" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
@@ -3308,13 +3366,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -3322,13 +3380,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -3336,13 +3394,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -3350,13 +3408,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -3364,13 +3422,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -3378,13 +3436,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -3392,13 +3450,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -3406,13 +3464,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -3420,13 +3478,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -3434,13 +3492,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -3448,13 +3506,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -3462,13 +3520,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
@@ -3476,13 +3534,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
@@ -3490,13 +3548,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
@@ -3504,13 +3562,13 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -3545,7 +3603,7 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B1" s="47" t="s">
         <v>1</v>
@@ -3556,112 +3614,112 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="48" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="48" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="48" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="48" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="48" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="48" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="48" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="48" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3685,10 +3743,10 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="44" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -3696,7 +3754,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -3704,7 +3762,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -3712,7 +3770,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -3720,7 +3778,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -3728,7 +3786,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
@@ -3736,7 +3794,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -3744,7 +3802,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -3752,7 +3810,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -3760,7 +3818,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -3768,7 +3826,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -3776,7 +3834,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -3784,7 +3842,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -3792,7 +3850,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -3800,7 +3858,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -3808,7 +3866,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -3816,7 +3874,23 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>306</v>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="31">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -3843,10 +3917,10 @@
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
       <c r="A1" s="44" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -4217,7 +4291,71 @@
         <v>20.0</v>
       </c>
     </row>
-    <row r="48" ht="22.5" customHeight="1"/>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B48" s="31">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B49" s="31">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B50" s="31">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B51" s="31">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B52" s="31">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="31">
+        <v>18.0</v>
+      </c>
+      <c r="B53" s="31">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="31">
+        <v>18.0</v>
+      </c>
+      <c r="B54" s="31">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="31">
+        <v>18.0</v>
+      </c>
+      <c r="B55" s="31">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="56" ht="22.5" customHeight="1"/>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4239,10 +4377,10 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="44" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -4453,7 +4591,39 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1"/>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="31">
+        <v>17.0</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="31">
+        <v>18.0</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="31">
+        <v>18.0</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1"/>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
